--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29da198aaee83e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa431a0f71f59764</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7cadb668678f16</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,32 +1528,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Java Technical Architect</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,15 +1563,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Kafka, Oracle, SQL Server, CI/CD, Azure DevOps, Maven</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,40 +1581,670 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7747f31dfec5b3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Mainframe Cloud Integration Specialist</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Java Consultant</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior API Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>AI Application Architect</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CrowdStrike Security Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Cloud-Native MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HI, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>API Enablement Specialist</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>API Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Java Technical Architect</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Kafka, Oracle, SQL Server, CI/CD, Azure DevOps, Maven</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7747f31dfec5b3b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>IL, US USA</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D52" t="n">
         <v>10.4</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
         </is>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,24 +556,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58d7fa4052fcb61</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,15 +618,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a961034c94203e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,15 +653,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=5360f2e4e078cc82</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
@@ -723,15 +723,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Google Cloud Platform, Scala, Kafka, DynamoDB</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b77b0819d9ee2a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
+          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior DB2 DBA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=30310d1133432e87</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Google Cloud Platform, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=8b77b0819d9ee2a7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, Azure, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2844c76b7de91d2</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,15 +1738,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
+          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1773,15 +1773,15 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1808,15 +1808,15 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1878,50 +1878,50 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,15 +1948,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,15 +1983,15 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbcbfd38f811d9a</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16ccbca862f6e0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98cdc967317969d8</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,32 +2123,32 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78e22e0760c3febd</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,50 +2158,50 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Technical Architect</t>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Kafka, Oracle, SQL Server, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7747f31dfec5b3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,15 +2236,260 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>JCL Developer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>API Enablement Specialist</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Java Technical Architect</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Kafka, Oracle, SQL Server, CI/CD, Azure DevOps, Maven</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7747f31dfec5b3b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
         </is>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -748,7 +748,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DB2 DBA</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Google Cloud Platform, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30310d1133432e87</t>
+          <t>https://www.indeed.com/viewjob?jk=8b77b0819d9ee2a7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Senior DB2 DBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Google Cloud Platform, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b77b0819d9ee2a7</t>
+          <t>https://www.indeed.com/viewjob?jk=30310d1133432e87</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
+          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,15 +2123,15 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,52 +2201,52 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JCL Developer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,24 +2306,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>JCL Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>API Enablement Specialist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,15 +2481,50 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
         </is>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
+          <t>https://www.indeed.com/viewjob?jk=db40aa076d14f9d0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,32 +513,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,32 +548,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a961034c94203e</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5360f2e4e078cc82</t>
+          <t>https://www.indeed.com/viewjob?jk=28e4d6385751ba88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9a21d31f3763d7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a961034c94203e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=5360f2e4e078cc82</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,15 +793,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Google Cloud Platform, Scala, Kafka, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b77b0819d9ee2a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,15 +898,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DB2 DBA</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30310d1133432e87</t>
+          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Google Cloud Platform, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=8b77b0819d9ee2a7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior DB2 DBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=30310d1133432e87</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,77 +1851,77 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,15 +1948,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,15 +1983,15 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,15 +2018,15 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2057,11 +2057,11 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
+          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2092,38 +2092,38 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,24 +2131,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,15 +2158,15 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,50 +2193,50 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,84 +2246,84 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JCL Developer</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,15 +2333,15 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
+          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,15 +2403,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java Technical Architect</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,15 +2438,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Kafka, Oracle, SQL Server, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7747f31dfec5b3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,60 +2473,445 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Memorial Sloan Kettering Cancer Center</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>San Ramon, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>JCL Developer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Java Technical Architect</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Kafka, Oracle, SQL Server, CI/CD, Azure DevOps, Maven</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7747f31dfec5b3b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>AI Application Architect</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cb8af80af373eb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
         <is>
           <t>IL, US USA</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D68" t="n">
         <v>10.4</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Cloud AI Consultant</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>API Enablement Specialist</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,15 +723,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a961034c94203e</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5360f2e4e078cc82</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
+          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,15 +898,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Google Cloud Platform, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8b77b0819d9ee2a7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Google Cloud Platform, Scala, Kafka, DynamoDB</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b77b0819d9ee2a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
+          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DB2 DBA</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30310d1133432e87</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Java Production Support Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,24 +1991,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,49 +2036,49 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,24 +2131,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,24 +2201,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
         </is>
       </c>
     </row>
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
+          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
+          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
+          <t>https://www.indeed.com/viewjob?jk=2658676db3cb0781</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,234 +2411,234 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=526fd8654b3fe27a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=aa04dfb29f5bfb80</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4d72b7fb4fe3c9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
+          <t>https://www.indeed.com/viewjob?jk=2486e9292dfc22af</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a64862baf27c704</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JCL Developer</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,50 +2648,50 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java Technical Architect</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,15 +2718,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Kafka, Oracle, SQL Server, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,182 +2736,567 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7747f31dfec5b3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cb8af80af373eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=5097254ffda8aa23</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=8ba1788435dbf136</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud AI Consultant</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
+          <t>https://www.indeed.com/viewjob?jk=179cc696ce6a3a5a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a49578296052b0f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ea6c9de4c26d6a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68fc2220156f231f</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>San Ramon, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>API Enablement Specialist</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>VA, US USA</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D76" t="n">
         <v>10.4</v>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>JCL Developer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Java Technical Architect</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Kafka, Oracle, SQL Server, CI/CD, Azure DevOps, Maven</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7747f31dfec5b3b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cb8af80af373eb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Cloud AI Consultant</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40aa076d14f9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,32 +548,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225ad27d76e606c</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,15 +618,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,15 +653,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e4d6385751ba88</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9a21d31f3763d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,15 +723,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1461d722d5f55c</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7cf1948628d7ab7</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Google Cloud Platform, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b77b0819d9ee2a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,77 +1641,77 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1812,173 +1812,173 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=2658676db3cb0781</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java Production Support Engineer</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Spark, Scala, Spark Streaming, Kafka, NoSQL, ETL, CI/CD</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1523381740d92013</t>
+          <t>https://www.indeed.com/viewjob?jk=526fd8654b3fe27a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=aa04dfb29f5bfb80</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67700eaac27ee1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4d72b7fb4fe3c9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1987,11 +1987,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,59 +2001,59 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=2486e9292dfc22af</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
+          <t>https://www.indeed.com/viewjob?jk=9a64862baf27c704</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,24 +2061,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,15 +2158,15 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,189 +2176,189 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=5097254ffda8aa23</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
+          <t>https://www.indeed.com/viewjob?jk=8ba1788435dbf136</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
+          <t>https://www.indeed.com/viewjob?jk=179cc696ce6a3a5a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a49578296052b0f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea6c9de4c26d6a0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2658676db3cb0781</t>
+          <t>https://www.indeed.com/viewjob?jk=68fc2220156f231f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526fd8654b3fe27a</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,119 +2456,119 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa04dfb29f5bfb80</t>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>API Enablement Specialist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4d72b7fb4fe3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2486e9292dfc22af</t>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a64862baf27c704</t>
+          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>JCL Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,15 +2578,15 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,707 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Cloud-Native MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Java Software Engineer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>HI, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e96f791ed6e1185</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Bioinformatics Software Engineer III, Pathology and Lab Medicine</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Memorial Sloan Kettering Cancer Center</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a671a473550229c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Cloud AI Application Administrator</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=474ce0b5b42f1022</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5097254ffda8aa23</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ba1788435dbf136</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=179cc696ce6a3a5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a49578296052b0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea6c9de4c26d6a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68fc2220156f231f</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>API Enablement Specialist</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>JCL Developer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Java Technical Architect</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Kafka, Oracle, SQL Server, CI/CD, Azure DevOps, Maven</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7747f31dfec5b3b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cb8af80af373eb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Cloud AI Consultant</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>NC, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, NoSQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e830061c496f86e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,24 +1711,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2658676db3cb0781</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526fd8654b3fe27a</t>
+          <t>https://www.indeed.com/viewjob?jk=2658676db3cb0781</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa04dfb29f5bfb80</t>
+          <t>https://www.indeed.com/viewjob?jk=526fd8654b3fe27a</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4d72b7fb4fe3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=aa04dfb29f5bfb80</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2486e9292dfc22af</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4d72b7fb4fe3c9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a64862baf27c704</t>
+          <t>https://www.indeed.com/viewjob?jk=2486e9292dfc22af</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,24 +2061,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=9a64862baf27c704</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
+          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2162,11 +2162,11 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5097254ffda8aa23</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ba1788435dbf136</t>
+          <t>https://www.indeed.com/viewjob?jk=5097254ffda8aa23</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179cc696ce6a3a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ba1788435dbf136</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a49578296052b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=179cc696ce6a3a5a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea6c9de4c26d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a49578296052b0f</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fc2220156f231f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea6c9de4c26d6a0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=68fc2220156f231f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,24 +2481,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>API Enablement Specialist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JCL Developer</t>
+          <t>Generative AI Operations Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,15 +2586,85 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>JCL Developer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
         </is>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Azure Data Architect – Fabric | Synapse | Lakehouse | Enterprise Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Corza Medical</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=50cc99cfa1b160e1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,24 +1781,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2658676db3cb0781</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526fd8654b3fe27a</t>
+          <t>https://www.indeed.com/viewjob?jk=2658676db3cb0781</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa04dfb29f5bfb80</t>
+          <t>https://www.indeed.com/viewjob?jk=526fd8654b3fe27a</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4d72b7fb4fe3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=aa04dfb29f5bfb80</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2486e9292dfc22af</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4d72b7fb4fe3c9</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a64862baf27c704</t>
+          <t>https://www.indeed.com/viewjob?jk=2486e9292dfc22af</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=9a64862baf27c704</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,24 +2131,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,15 +2193,15 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5097254ffda8aa23</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ba1788435dbf136</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179cc696ce6a3a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=5097254ffda8aa23</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a49578296052b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ba1788435dbf136</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea6c9de4c26d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=179cc696ce6a3a5a</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fc2220156f231f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a49578296052b0f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea6c9de4c26d6a0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Senior Taxonomist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=68fc2220156f231f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,24 +2551,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Generative AI Operations Engineer</t>
+          <t>API Enablement Specialist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
         </is>
       </c>
     </row>
@@ -2667,6 +2667,76 @@
       <c r="G64" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Generative AI Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,42 +503,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
@@ -583,11 +583,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,49 +636,49 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Cloud Data Platform Administrator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>natumatic inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=53c6decd13829199</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azure Data Architect – Fabric | Synapse | Lakehouse | Enterprise Platform</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Corza Medical</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,24 +1606,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50cc99cfa1b160e1</t>
+          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
         </is>
       </c>
     </row>
@@ -1693,52 +1693,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2658676db3cb0781</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526fd8654b3fe27a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa04dfb29f5bfb80</t>
+          <t>https://www.indeed.com/viewjob?jk=2658676db3cb0781</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4d72b7fb4fe3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=526fd8654b3fe27a</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2486e9292dfc22af</t>
+          <t>https://www.indeed.com/viewjob?jk=aa04dfb29f5bfb80</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a64862baf27c704</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4d72b7fb4fe3c9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=2486e9292dfc22af</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,24 +2166,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=9a64862baf27c704</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
+          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Merrifield, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2591,19 +2591,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>API Enablement Specialist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JCL Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
         </is>
       </c>
     </row>
@@ -2737,6 +2737,41 @@
       <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>JCL Developer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -496,84 +496,84 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
+          <t>https://www.indeed.com/viewjob?jk=db40aa076d14f9d0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
@@ -618,11 +618,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -636,49 +636,49 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>natumatic inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c6decd13829199</t>
+          <t>https://www.indeed.com/viewjob?jk=28e4d6385751ba88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=9d9a21d31f3763d7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,15 +723,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a961034c94203e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,49 +776,49 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
+          <t>https://www.indeed.com/viewjob?jk=5360f2e4e078cc82</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Mainframe System Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Noblesoft Technologies Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=cdfd9ffe1f4bab35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Cloud Data Platform Administrator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>natumatic inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=53c6decd13829199</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Google Cloud Platform, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b77b0819d9ee2a7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior DB2 DBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=30310d1133432e87</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,137 +1721,137 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,137 +1931,137 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2658676db3cb0781</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526fd8654b3fe27a</t>
+          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa04dfb29f5bfb80</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4d72b7fb4fe3c9</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2486e9292dfc22af</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Enterprise Ontologist</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a64862baf27c704</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,15 +2263,15 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,242 +2281,242 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5097254ffda8aa23</t>
+          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ba1788435dbf136</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179cc696ce6a3a5a</t>
+          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a49578296052b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea6c9de4c26d6a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Taxonomist</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fc2220156f231f</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=2658676db3cb0781</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=526fd8654b3fe27a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Merrifield, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,182 +2596,812 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
+          <t>https://www.indeed.com/viewjob?jk=aa04dfb29f5bfb80</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4d72b7fb4fe3c9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
+          <t>https://www.indeed.com/viewjob?jk=2486e9292dfc22af</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Generative AI Operations Engineer</t>
+          <t>Senior Enterprise Ontologist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+          <t>https://www.indeed.com/viewjob?jk=9a64862baf27c704</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BITS, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>Cloud-Native MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5097254ffda8aa23</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ba1788435dbf136</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=179cc696ce6a3a5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a49578296052b0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ea6c9de4c26d6a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68fc2220156f231f</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>San Ramon, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>JCL Developer</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>TX, US USA</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D76" t="n">
         <v>10.4</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Java Technical Architect</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Kafka, Oracle, SQL Server, CI/CD, Azure DevOps, Maven</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7747f31dfec5b3b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Generative AI Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cb8af80af373eb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>The Nehr Agency</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Progressive Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Merrifield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>API Enablement Specialist</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -496,84 +496,84 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40aa076d14f9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
@@ -618,11 +618,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e4d6385751ba88</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9a21d31f3763d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,15 +723,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a961034c94203e</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,49 +776,49 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5360f2e4e078cc82</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mainframe System Engineer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Noblesoft Technologies Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdfd9ffe1f4bab35</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>natumatic inc</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c6decd13829199</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Google Cloud Platform, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b77b0819d9ee2a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DB2 DBA</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30310d1133432e87</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,147 +1676,147 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,28 +1917,28 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,15 +1948,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,49 +1966,49 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BITS, Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>The Nehr Agency</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Merrifield, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>API Enablement Specialist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,15 +2193,15 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,15 +2228,15 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Generative AI Operations Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,15 +2263,15 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,15 +2298,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
+          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>JCL Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,15 +2333,15 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,1057 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>CrowdStrike Security Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Enterprise Ontologist</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2658676db3cb0781</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Senior Enterprise Ontologist</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=526fd8654b3fe27a</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior Enterprise Ontologist</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa04dfb29f5bfb80</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Senior Enterprise Ontologist</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4d72b7fb4fe3c9</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Enterprise Ontologist</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2486e9292dfc22af</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Senior Enterprise Ontologist</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a64862baf27c704</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>BITS, Inc.</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Cloud-Native MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5097254ffda8aa23</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ba1788435dbf136</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=179cc696ce6a3a5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a49578296052b0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea6c9de4c26d6a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Scala, Kafka, Data Modeling, ETL, ELT, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68fc2220156f231f</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>JCL Developer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2391611035d932e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Java Technical Architect</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Kafka, Oracle, SQL Server, CI/CD, Azure DevOps, Maven</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7747f31dfec5b3b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Generative AI Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cb8af80af373eb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>The Nehr Agency</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Progressive Technology Solutions</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Merrifield, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>API Enablement Specialist</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>AI Integration Engineer (Java + AI)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -608,42 +608,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>(1363) Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=f7b52733c5b93b90</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d390ec06d924f3da</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -818,52 +818,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, Hadoop</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25850899276cb6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BITS, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,52 +1991,52 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>API Enablement Specialist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Merrifield, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2171,19 +2171,19 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Generative AI Operations Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>JCL Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2245,111 +2245,6 @@
         </is>
       </c>
       <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=713151b0e6387311</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Generative AI Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, NoSQL, MLOps, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>JCL Developer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
         </is>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,112 +468,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Senior Data Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stellix</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Foxborough, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
+          <t>https://www.indeed.com/viewjob?jk=23da0426139b73c0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(1363) Senior DevOps Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b52733c5b93b90</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,24 +661,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,104 +836,104 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,99 +1676,99 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,24 +1921,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1987,11 +1987,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,129 +2001,129 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Nehr Agency</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Generative AI Operations Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JCL Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Nehr Agency</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,15 +2236,155 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>API Enablement Specialist</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Generative AI Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>JCL Developer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
         </is>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FusionStak LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
+          <t>https://www.indeed.com/viewjob?jk=3092577afd5b3438</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=48a3d37ec6e3c854</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,172 +601,172 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=8b28a5e5f471429b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=fa0174c36940aa83</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=f105011f4f992e1c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,137 +776,137 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=458abf73283f2111</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=bf45dfb6778c0fdc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=86e2ec9b122daeb5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9733f64d96e7aa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=a02052c69a3c492c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=94ec53f54f9c7088</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,347 +986,347 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd4bc382e9c7b62</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=0888715b72dfc054</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=509c8ac8509a5876</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac494b36ae187df</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=0f3909b266a9e56c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5765fb327aec80</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0446823f314c2a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=53455cd5c2762916</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a722531933fefd7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Big Data Developer / Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=ff174cdafd94cad6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,137 +1371,137 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=20ebbd1659adab31</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Togetherwork</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,102 +1826,102 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,172 +2106,172 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Nehr Agency</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Generative AI Operations Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,40 +2351,950 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Data Engineer - Remote, USA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Bluelight Consulting</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote, USA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Bluelight Consulting</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Charleston, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote, USA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Bluelight Consulting</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Billings, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote, USA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Bluelight Consulting</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote, USA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Bluelight Consulting</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote, USA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Bluelight Consulting</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Mainframe Cloud Integration Specialist</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SALOMON</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Kubernetes ML Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Back-End AI Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>RightRev</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CrowdStrike Security Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Cloud-Native MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=902ef08f4a0d7d10</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Tech-assist</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>San Ramon, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>The Nehr Agency</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>API Enablement Specialist</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Generative AI Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>JCL Developer</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D82" t="n">
         <v>10.4</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
         </is>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b28a5e5f471429b</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa0174c36940aa83</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f105011f4f992e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=20ebbd1659adab31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Togetherwork</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458abf73283f2111</t>
+          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf45dfb6778c0fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86e2ec9b122daeb5</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9733f64d96e7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a02052c69a3c492c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ec53f54f9c7088</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,137 +986,137 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd4bc382e9c7b62</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0888715b72dfc054</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=509c8ac8509a5876</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac494b36ae187df</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f3909b266a9e56c</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5765fb327aec80</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,137 +1196,137 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0446823f314c2a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53455cd5c2762916</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a722531933fefd7</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Big Data Developer / Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Hadoop, HDFS, Hive, HBase, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff174cdafd94cad6</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,137 +1371,137 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ebbd1659adab31</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Togetherwork</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,147 +1991,147 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,102 +2211,102 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,277 +2351,277 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=902ef08f4a0d7d10</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Git, Datadog</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=3847663034b7777f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>The Nehr Agency</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>API Enablement Specialist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2652,98 +2652,98 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Generative AI Operations Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>JCL Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2770,531 +2770,6 @@
         </is>
       </c>
       <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Associate ML Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Associate ML Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>CrowdStrike Security Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Cloud-Native MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior MuleSoft Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Green Irony</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=902ef08f4a0d7d10</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Tech-assist</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Infrastructure</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>The Nehr Agency</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>API Enablement Specialist</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>GenAI Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Generative AI Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>JCL Developer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
         </is>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>InformAI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,49 +636,49 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=86fc1393dcf5eb4a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ebbd1659adab31</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Togetherwork</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
+          <t>https://www.indeed.com/viewjob?jk=20ebbd1659adab31</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Togetherwork</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,24 +1046,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,77 +1116,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,77 +1991,77 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,84 +2071,84 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2337,11 +2337,11 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902ef08f4a0d7d10</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tech-assist</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3847663034b7777f</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Nehr Agency</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+          <t>https://www.indeed.com/viewjob?jk=902ef08f4a0d7d10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Generative AI Operations Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>JCL Developer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,332 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Cloud Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Fueled</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3847663034b7777f</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Advancement Technical Systems Developer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Syracuse University</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Syracuse, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Generative AI Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>The Nehr Agency</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>API Enablement Specialist</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>JCL Developer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Verisign</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, YARN, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3b1f0870e48cb0f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>InformAI</t>
+          <t>The Brite Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fc1393dcf5eb4a</t>
+          <t>https://www.indeed.com/viewjob?jk=97fe4fefddbc3bf0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>InformAI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,49 +671,49 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=86fc1393dcf5eb4a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ebbd1659adab31</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Togetherwork</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
+          <t>https://www.indeed.com/viewjob?jk=20ebbd1659adab31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Togetherwork</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,24 +2306,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>SPIGEN Inc. Multi-Position</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KOTRA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf57e231909db50</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,94 +2561,94 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902ef08f4a0d7d10</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tech-assist</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=902ef08f4a0d7d10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3847663034b7777f</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Advancement Technical Systems Developer</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Generative AI Operations Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Nehr Agency</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Senior Cloud Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Detroit Labs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=91754b3495fa2534</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>JCL Developer</t>
+          <t>Cloud Solutions Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fueled</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Git, Datadog</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+          <t>https://www.indeed.com/viewjob?jk=3847663034b7777f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Advancement Technical Systems Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,15 +3076,260 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Generative AI Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>The Nehr Agency</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>API Enablement Specialist</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>JCL Developer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Data Warehouse Applications Technician</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Salient</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Corning, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9664037f99ce3959</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Verisign</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>AWS, RDS, YARN, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d3b1f0870e48cb0f</t>
         </is>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer Sr Level - Connected Systems</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FusionStak LLC</t>
+          <t>Pratt Miller</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3092577afd5b3438</t>
+          <t>https://www.indeed.com/viewjob?jk=0e51e277a7646929</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>FusionStak LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a3d37ec6e3c854</t>
+          <t>https://www.indeed.com/viewjob?jk=3092577afd5b3438</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
+          <t>https://www.indeed.com/viewjob?jk=48a3d37ec6e3c854</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Brite Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fe4fefddbc3bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>InformAI</t>
+          <t>The Brite Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fc1393dcf5eb4a</t>
+          <t>https://www.indeed.com/viewjob?jk=97fe4fefddbc3bf0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>InformAI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=86fc1393dcf5eb4a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ebbd1659adab31</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4bead3a549cf5d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Togetherwork</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,77 +836,77 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>Togetherwork</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Musco Sports Lighting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,129 +1046,129 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Cloud Data Platform Administrator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>natumatic inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=53c6decd13829199</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>DevOps Architect - Mainframe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Web Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Palomar College</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1896fbf8cbc6af76</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,112 +2166,112 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,129 +2281,129 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=49c55bb99b922dcc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Mainframe Cloud Integration Specialist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SPIGEN Inc. Multi-Position</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KOTRA</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf57e231909db50</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,24 +2586,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>SPIGEN Inc. Multi-Position</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>KOTRA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf57e231909db50</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>Selenium Automation Tester</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>ASTRELUX IT INC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3299fc75914979c2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,102 +2771,102 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902ef08f4a0d7d10</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tech-assist</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>CrowdStrike Security Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Software Development Intern</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, SQL Server, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7bab82316f7860</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Architect</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Detroit Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91754b3495fa2534</t>
+          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fueled</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Git, Datadog</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,84 +3051,84 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3847663034b7777f</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Advancement Technical Systems Developer</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Generative AI Operations Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3142,11 +3142,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Nehr Agency</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,102 +3191,102 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>API Enablement Specialist</t>
+          <t>Senior Backend Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e334b20b2a1ff39</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>JCL Developer</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+          <t>https://www.indeed.com/viewjob?jk=902ef08f4a0d7d10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Warehouse Applications Technician</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Salient</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Corning, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9664037f99ce3959</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,15 +3321,575 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>San Ramon, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Ibotta</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Dorman Products</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Colmar, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cloud Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Fueled</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3847663034b7777f</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Infrastructure (Federal)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83b8886c05003079</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>JCL Developer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Advancement Technical Systems Developer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Syracuse University</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Syracuse, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>The Nehr Agency</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>API Enablement Specialist</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ERP &amp; Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Missouri State University</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15642f633949cc32</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Generative AI Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Warehouse Applications Technician</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Salient</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Corning, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Azure, BigQuery, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9664037f99ce3959</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Verisign</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>AWS, RDS, YARN, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d3b1f0870e48cb0f</t>
         </is>

--- a/results/job_matches_2026-03-09.xlsx
+++ b/results/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,60 +608,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Brite Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
+          <t>https://www.indeed.com/viewjob?jk=97fe4fefddbc3bf0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Brite Group</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fe4fefddbc3bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>InformAI</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fc1393dcf5eb4a</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4bead3a549cf5d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,24 +801,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4bead3a549cf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=340a535ec0c84cac</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Togetherwork</t>
+          <t>Musco Sports Lighting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Musco Sports Lighting</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Engineer-Audience Data Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>natumatic inc</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c6decd13829199</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Architect - Mainframe</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Splunk, Jenkins, Azure DevOps, Maven</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b82583635e22429</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07501398d0e8a4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Web Developer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Palomar College</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Scala, SQL Server</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1896fbf8cbc6af76</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Kafka, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Remote, USA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd6ddbd121342d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Billings, MT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,199 +2096,199 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49c55bb99b922dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mainframe Cloud Integration Specialist</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b2adadaa402ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Software Development Intern</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,112 +2551,112 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, SQL Server, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7bab82316f7860</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SPIGEN Inc. Multi-Position</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KOTRA</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf57e231909db50</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Selenium Automation Tester</t>
+          <t>Senior Software Engineer, DataOps &amp; Platform Services</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ASTRELUX IT INC</t>
+          <t>Anheuser-Busch</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3299fc75914979c2</t>
+          <t>https://www.indeed.com/viewjob?jk=3726b62a784e7a79</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,102 +2771,102 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, ETL, REST API integration, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966c6a4905b91bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Development Intern</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, SQL Server, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7bab82316f7860</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Distinctive Staffing Solutions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, Docker, Airflow, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=88f7a8640bb1fab0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>The Nehr Agency</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3142,11 +3142,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Splunk, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,742 +3156,77 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119f9ca723edb406</t>
+          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>JCL Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Backend Developer</t>
+          <t>Advancement Technical Systems Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e334b20b2a1ff39</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior MuleSoft Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Green Irony</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=902ef08f4a0d7d10</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Engineer – Software Development</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Suvida Healthcare</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Tech-assist</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Ibotta</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Sr. Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Dorman Products</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Colmar, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Infrastructure</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Cloud Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Fueled</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3847663034b7777f</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Infrastructure (Federal)</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83b8886c05003079</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>GenAI Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>JCL Developer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Advancement Technical Systems Developer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Syracuse University</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Syracuse, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>The Nehr Agency</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>API Enablement Specialist</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>ERP &amp; Database Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Missouri State University</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15642f633949cc32</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Generative AI Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Warehouse Applications Technician</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Salient</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Corning, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, Azure, BigQuery, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9664037f99ce3959</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Verisign</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, YARN, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b1f0870e48cb0f</t>
         </is>
       </c>
     </row>
